--- a/ert/input/distributions/design_matrix_one_by_one.xlsx
+++ b/ert/input/distributions/design_matrix_one_by_one.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DesignSheet01" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DefaultValues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6035,10 +6036,10 @@
         <v>1640</v>
       </c>
       <c r="G72" t="n">
-        <v>1680.23</v>
+        <v>1680.53</v>
       </c>
       <c r="H72" t="n">
-        <v>1664.13</v>
+        <v>1656.18</v>
       </c>
       <c r="I72" t="n">
         <v>100</v>
@@ -6113,10 +6114,10 @@
         <v>1640</v>
       </c>
       <c r="G73" t="n">
-        <v>1674.19</v>
+        <v>1678.76</v>
       </c>
       <c r="H73" t="n">
-        <v>1662.71</v>
+        <v>1659.58</v>
       </c>
       <c r="I73" t="n">
         <v>100</v>
@@ -6191,10 +6192,10 @@
         <v>1640</v>
       </c>
       <c r="G74" t="n">
-        <v>1672.31</v>
+        <v>1679.91</v>
       </c>
       <c r="H74" t="n">
-        <v>1657.88</v>
+        <v>1661.79</v>
       </c>
       <c r="I74" t="n">
         <v>100</v>
@@ -6269,10 +6270,10 @@
         <v>1640</v>
       </c>
       <c r="G75" t="n">
-        <v>1677.46</v>
+        <v>1674.1</v>
       </c>
       <c r="H75" t="n">
-        <v>1659.15</v>
+        <v>1663.59</v>
       </c>
       <c r="I75" t="n">
         <v>100</v>
@@ -6347,10 +6348,10 @@
         <v>1640</v>
       </c>
       <c r="G76" t="n">
-        <v>1673.54</v>
+        <v>1672.74</v>
       </c>
       <c r="H76" t="n">
-        <v>1658.31</v>
+        <v>1664.94</v>
       </c>
       <c r="I76" t="n">
         <v>100</v>
@@ -6425,10 +6426,10 @@
         <v>1640</v>
       </c>
       <c r="G77" t="n">
-        <v>1673.87</v>
+        <v>1675.51</v>
       </c>
       <c r="H77" t="n">
-        <v>1658.66</v>
+        <v>1657.52</v>
       </c>
       <c r="I77" t="n">
         <v>100</v>
@@ -6503,10 +6504,10 @@
         <v>1640</v>
       </c>
       <c r="G78" t="n">
-        <v>1676.22</v>
+        <v>1677.87</v>
       </c>
       <c r="H78" t="n">
-        <v>1658.12</v>
+        <v>1662.34</v>
       </c>
       <c r="I78" t="n">
         <v>100</v>
@@ -6581,10 +6582,10 @@
         <v>1640</v>
       </c>
       <c r="G79" t="n">
-        <v>1678.06</v>
+        <v>1673.25</v>
       </c>
       <c r="H79" t="n">
-        <v>1660.8</v>
+        <v>1658.21</v>
       </c>
       <c r="I79" t="n">
         <v>100</v>
@@ -6659,10 +6660,10 @@
         <v>1640</v>
       </c>
       <c r="G80" t="n">
-        <v>1676.92</v>
+        <v>1676.22</v>
       </c>
       <c r="H80" t="n">
-        <v>1656.13</v>
+        <v>1655.66</v>
       </c>
       <c r="I80" t="n">
         <v>100</v>
@@ -6737,10 +6738,10 @@
         <v>1640</v>
       </c>
       <c r="G81" t="n">
-        <v>1678.44</v>
+        <v>1681.52</v>
       </c>
       <c r="H81" t="n">
-        <v>1658.26</v>
+        <v>1660.77</v>
       </c>
       <c r="I81" t="n">
         <v>100</v>
@@ -13085,16 +13086,16 @@
         <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>0.1835</v>
+        <v>0.00068</v>
       </c>
       <c r="R162" t="n">
-        <v>0.00046</v>
+        <v>0.00044</v>
       </c>
       <c r="S162" t="n">
-        <v>2e-05</v>
+        <v>6e-05</v>
       </c>
       <c r="T162" t="n">
-        <v>0.00067</v>
+        <v>0.01732</v>
       </c>
       <c r="U162" t="n">
         <v>0.34</v>
@@ -13163,16 +13164,16 @@
         <v>0</v>
       </c>
       <c r="Q163" t="n">
-        <v>6.999999999999999e-05</v>
+        <v>0.05785</v>
       </c>
       <c r="R163" t="n">
-        <v>0.00818</v>
+        <v>0.08487</v>
       </c>
       <c r="S163" t="n">
-        <v>2e-05</v>
+        <v>0.0053</v>
       </c>
       <c r="T163" t="n">
-        <v>0.007979999999999999</v>
+        <v>1e-05</v>
       </c>
       <c r="U163" t="n">
         <v>0.34</v>
@@ -13241,16 +13242,16 @@
         <v>0</v>
       </c>
       <c r="Q164" t="n">
-        <v>0.00258</v>
+        <v>0.11288</v>
       </c>
       <c r="R164" t="n">
-        <v>0.02494</v>
+        <v>0.4624</v>
       </c>
       <c r="S164" t="n">
-        <v>0.00267</v>
+        <v>0.49546</v>
       </c>
       <c r="T164" t="n">
-        <v>0.00297</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="U164" t="n">
         <v>0.34</v>
@@ -13319,16 +13320,16 @@
         <v>0</v>
       </c>
       <c r="Q165" t="n">
-        <v>0.00569</v>
+        <v>0.0167</v>
       </c>
       <c r="R165" t="n">
-        <v>0.00529</v>
+        <v>0.00805</v>
       </c>
       <c r="S165" t="n">
-        <v>1e-05</v>
+        <v>0.03711</v>
       </c>
       <c r="T165" t="n">
-        <v>0.13275</v>
+        <v>0.00309</v>
       </c>
       <c r="U165" t="n">
         <v>0.34</v>
@@ -13397,16 +13398,16 @@
         <v>0</v>
       </c>
       <c r="Q166" t="n">
-        <v>0.01029</v>
+        <v>0.00019</v>
       </c>
       <c r="R166" t="n">
-        <v>0.36596</v>
+        <v>0.10484</v>
       </c>
       <c r="S166" t="n">
-        <v>0.01503</v>
+        <v>0.01874</v>
       </c>
       <c r="T166" t="n">
-        <v>0.00328</v>
+        <v>0.04436</v>
       </c>
       <c r="U166" t="n">
         <v>0.34</v>
@@ -13475,16 +13476,16 @@
         <v>0</v>
       </c>
       <c r="Q167" t="n">
-        <v>0.00151</v>
+        <v>0.41671</v>
       </c>
       <c r="R167" t="n">
-        <v>0.08152</v>
+        <v>0.00163</v>
       </c>
       <c r="S167" t="n">
-        <v>0.0185</v>
+        <v>0.00107</v>
       </c>
       <c r="T167" t="n">
-        <v>0.02261</v>
+        <v>0.00016</v>
       </c>
       <c r="U167" t="n">
         <v>0.34</v>
@@ -13553,16 +13554,16 @@
         <v>0</v>
       </c>
       <c r="Q168" t="n">
-        <v>0.0023</v>
+        <v>0.00254</v>
       </c>
       <c r="R168" t="n">
-        <v>0.0358</v>
+        <v>0.01021</v>
       </c>
       <c r="S168" t="n">
-        <v>0.06886</v>
+        <v>0.13226</v>
       </c>
       <c r="T168" t="n">
-        <v>0.0017</v>
+        <v>0.00655</v>
       </c>
       <c r="U168" t="n">
         <v>0.34</v>
@@ -13631,16 +13632,16 @@
         <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>0.2138</v>
+        <v>2e-05</v>
       </c>
       <c r="R169" t="n">
-        <v>3e-05</v>
+        <v>0.00027</v>
       </c>
       <c r="S169" t="n">
-        <v>0.00018</v>
+        <v>0.00081</v>
       </c>
       <c r="T169" t="n">
-        <v>2e-05</v>
+        <v>0.25607</v>
       </c>
       <c r="U169" t="n">
         <v>0.34</v>
@@ -13709,16 +13710,16 @@
         <v>0</v>
       </c>
       <c r="Q170" t="n">
-        <v>0.00488</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="R170" t="n">
-        <v>0.57709</v>
+        <v>2e-05</v>
       </c>
       <c r="S170" t="n">
-        <v>6e-05</v>
+        <v>2e-05</v>
       </c>
       <c r="T170" t="n">
-        <v>0.08429</v>
+        <v>0.93989</v>
       </c>
       <c r="U170" t="n">
         <v>0.34</v>
@@ -13787,16 +13788,16 @@
         <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>0.00265</v>
+        <v>0.00641</v>
       </c>
       <c r="R171" t="n">
-        <v>0.00013</v>
+        <v>4e-05</v>
       </c>
       <c r="S171" t="n">
-        <v>0.33315</v>
+        <v>0.00019</v>
       </c>
       <c r="T171" t="n">
-        <v>0.76886</v>
+        <v>0.001</v>
       </c>
       <c r="U171" t="n">
         <v>0.34</v>
@@ -20062,7 +20063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20952,7 +20953,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -20972,7 +20973,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="92">
@@ -20982,7 +20983,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>6000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="93">
@@ -21002,7 +21003,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row r="95">
@@ -21018,37 +21019,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>THERYS_APS_1_0_GF_GRF2_RESIDUAL_MAINRANGE</t>
+          <t>THERYS_APS_1_0_GF_GRF3_RESIDUAL_MAINRANGE</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>6000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>THERYS_APS_1_0_GF_GRF2_RESIDUAL_PERPRANGE</t>
+          <t>THERYS_APS_1_0_GF_GRF3_RESIDUAL_PERPRANGE</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>THERYS_APS_1_0_GF_GRF2_RESIDUAL_VERTRANGE</t>
+          <t>THERYS_APS_1_0_GF_GRF3_RESIDUAL_VERTRANGE</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>THERYS_APS_1_0_GF_GRF2_RESIDUAL_AZIMUTHANGLE</t>
+          <t>THERYS_APS_1_0_GF_GRF3_RESIDUAL_AZIMUTHANGLE</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -21058,211 +21059,181 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>THERYS_APS_1_0_GF_GRF3_RESIDUAL_MAINRANGE</t>
+          <t>VOLON_APS_1_0_GF_GRF1_RESIDUAL_MAINRANGE</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>THERYS_APS_1_0_GF_GRF3_RESIDUAL_PERPRANGE</t>
+          <t>VOLON_APS_1_0_GF_GRF1_RESIDUAL_PERPRANGE</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>THERYS_APS_1_0_GF_GRF3_RESIDUAL_VERTRANGE</t>
+          <t>VOLON_APS_1_0_GF_GRF1_RESIDUAL_VERTRANGE</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>THERYS_APS_1_0_GF_GRF3_RESIDUAL_AZIMUTHANGLE</t>
+          <t>VOLON_APS_1_0_GF_GRF1_RESIDUAL_AZIMUTHANGLE</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>VOLON_APS_1_0_GF_GRF1_RESIDUAL_MAINRANGE</t>
+          <t>VOLON_APS_1_0_GF_GRF3_RESIDUAL_MAINRANGE</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>VOLON_APS_1_0_GF_GRF1_RESIDUAL_PERPRANGE</t>
+          <t>VOLON_APS_1_0_GF_GRF3_RESIDUAL_PERPRANGE</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>VOLON_APS_1_0_GF_GRF1_RESIDUAL_VERTRANGE</t>
+          <t>VOLON_APS_1_0_GF_GRF3_RESIDUAL_VERTRANGE</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>VOLON_APS_1_0_GF_GRF1_RESIDUAL_AZIMUTHANGLE</t>
+          <t>VOLON_APS_1_0_GF_GRF3_RESIDUAL_AZIMUTHANGLE</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>VOLON_APS_1_0_GF_GRF2_RESIDUAL_MAINRANGE</t>
+          <t>WWIR_MULT_20180101_A5</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>VOLON_APS_1_0_GF_GRF2_RESIDUAL_PERPRANGE</t>
+          <t>WWIR_MULT_20190101_A5</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>VOLON_APS_1_0_GF_GRF2_RESIDUAL_VERTRANGE</t>
+          <t>WOPR_MULT_20180101_A1</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VOLON_APS_1_0_GF_GRF2_RESIDUAL_AZIMUTHANGLE</t>
+          <t>WWPR_MULT_20180101_A1</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>VOLON_APS_1_0_GF_GRF3_RESIDUAL_MAINRANGE</t>
+          <t>WGPR_MULT_20180101_A1</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>VOLON_APS_1_0_GF_GRF3_RESIDUAL_PERPRANGE</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>VOLON_APS_1_0_GF_GRF3_RESIDUAL_VERTRANGE</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>VOLON_APS_1_0_GF_GRF3_RESIDUAL_AZIMUTHANGLE</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>WWIR_MULT_20180101_A5</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>WWIR_MULT_20190101_A5</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>WOPR_MULT_20180101_A1</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>WWPR_MULT_20180101_A1</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>WGPR_MULT_20180101_A1</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Created using ert version:</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>26.0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Created on:</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:39:59+01:00</t>
+        </is>
       </c>
     </row>
   </sheetData>
